--- a/tool/kintone-resourse-generator/template/custom/L01.xlsx
+++ b/tool/kintone-resourse-generator/template/custom/L01.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\custom-template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\template\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213B5795-D0A7-4DEB-AED0-6027FAD1B6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6951BA72-E6E6-48D9-8E9A-89C991F72768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="space-settings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="29">
   <si>
     <t>管理者</t>
   </si>
@@ -105,6 +105,17 @@
   </si>
   <si>
     <t>ユーザ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スペース名</t>
+    <rPh sb="4" eb="5">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BBB</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -112,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -134,6 +145,11 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -161,11 +177,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -480,32 +498,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="68.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="68.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="b">
-        <v>1</v>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -514,6 +536,9 @@
         <v>1</v>
       </c>
       <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
